--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L734"/>
+  <dimension ref="A1:L735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31276,6 +31276,48 @@
       <c r="L734" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>339.28</v>
+      </c>
+      <c r="C735" t="n">
+        <v>333.97</v>
+      </c>
+      <c r="D735" t="n">
+        <v>340.58</v>
+      </c>
+      <c r="E735" t="n">
+        <v>357.48</v>
+      </c>
+      <c r="F735" t="n">
+        <v>345.53</v>
+      </c>
+      <c r="G735" t="n">
+        <v>339.51</v>
+      </c>
+      <c r="H735" t="n">
+        <v>339.38</v>
+      </c>
+      <c r="I735" t="n">
+        <v>345.9</v>
+      </c>
+      <c r="J735" t="n">
+        <v>350.9</v>
+      </c>
+      <c r="K735" t="n">
+        <v>358.2</v>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -31290,7 +31332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B739"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38683,6 +38725,16 @@
       </c>
       <c r="B739" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -38851,28 +38903,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4862108888061163</v>
+        <v>-0.4836320572353706</v>
       </c>
       <c r="J2" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K2" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1425232491664727</v>
+        <v>0.141421292308189</v>
       </c>
       <c r="M2" t="n">
-        <v>7.132708704285996</v>
+        <v>7.134915868652906</v>
       </c>
       <c r="N2" t="n">
-        <v>74.97209043405638</v>
+        <v>74.98306423417993</v>
       </c>
       <c r="O2" t="n">
-        <v>8.658642528367618</v>
+        <v>8.659276195744072</v>
       </c>
       <c r="P2" t="n">
-        <v>342.9256647602713</v>
+        <v>342.89855804581</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38929,28 +38981,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1967696713476078</v>
+        <v>-0.1964558732308434</v>
       </c>
       <c r="J3" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K3" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09368750860852104</v>
+        <v>0.0936724552865571</v>
       </c>
       <c r="M3" t="n">
-        <v>3.734912304538615</v>
+        <v>3.731278100724995</v>
       </c>
       <c r="N3" t="n">
-        <v>19.74359419225697</v>
+        <v>19.71837041774949</v>
       </c>
       <c r="O3" t="n">
-        <v>4.443376440529991</v>
+        <v>4.440537176710662</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0346628435058</v>
+        <v>338.0313644365659</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39007,28 +39059,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1679982189917932</v>
+        <v>-0.1672034102703393</v>
       </c>
       <c r="J4" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K4" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03806334476171913</v>
+        <v>0.03781984019277873</v>
       </c>
       <c r="M4" t="n">
-        <v>5.084204938803191</v>
+        <v>5.080915791375064</v>
       </c>
       <c r="N4" t="n">
-        <v>37.59780582526741</v>
+        <v>37.55732754334676</v>
       </c>
       <c r="O4" t="n">
-        <v>6.131704968870193</v>
+        <v>6.128403343722307</v>
       </c>
       <c r="P4" t="n">
-        <v>342.1838232475244</v>
+        <v>342.1754688232541</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39085,28 +39137,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0696696363005745</v>
+        <v>-0.06886923962471884</v>
       </c>
       <c r="J5" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K5" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01291983369521044</v>
+        <v>0.01266013926437759</v>
       </c>
       <c r="M5" t="n">
-        <v>3.448624531241383</v>
+        <v>3.448016295965834</v>
       </c>
       <c r="N5" t="n">
-        <v>19.54772446247756</v>
+        <v>19.53198918841714</v>
       </c>
       <c r="O5" t="n">
-        <v>4.421280862202441</v>
+        <v>4.41950101124744</v>
       </c>
       <c r="P5" t="n">
-        <v>356.4732312175655</v>
+        <v>356.464818056972</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39163,28 +39215,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2272745561223757</v>
+        <v>-0.2269348268136334</v>
       </c>
       <c r="J6" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K6" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08353130365254158</v>
+        <v>0.08353452317434107</v>
       </c>
       <c r="M6" t="n">
-        <v>4.267926239861523</v>
+        <v>4.264110285686952</v>
       </c>
       <c r="N6" t="n">
-        <v>29.87332972307765</v>
+        <v>29.83459346470155</v>
       </c>
       <c r="O6" t="n">
-        <v>5.465649981756758</v>
+        <v>5.462105222778261</v>
       </c>
       <c r="P6" t="n">
-        <v>350.2998551628687</v>
+        <v>350.2962841869776</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39241,28 +39293,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2939890417102478</v>
+        <v>-0.2932247772267718</v>
       </c>
       <c r="J7" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K7" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1314587104132856</v>
+        <v>0.1311807322398136</v>
       </c>
       <c r="M7" t="n">
-        <v>4.247331674502106</v>
+        <v>4.245272261428267</v>
       </c>
       <c r="N7" t="n">
-        <v>30.10072850721436</v>
+        <v>30.0696542506283</v>
       </c>
       <c r="O7" t="n">
-        <v>5.486413082079617</v>
+        <v>5.483580422554984</v>
       </c>
       <c r="P7" t="n">
-        <v>344.5297725740151</v>
+        <v>344.5217392075239</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39319,28 +39371,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1376492242765868</v>
+        <v>-0.1370901253732194</v>
       </c>
       <c r="J8" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K8" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03622381695218535</v>
+        <v>0.03604129867650385</v>
       </c>
       <c r="M8" t="n">
-        <v>4.023339231756944</v>
+        <v>4.020951806549372</v>
       </c>
       <c r="N8" t="n">
-        <v>26.57315590550445</v>
+        <v>26.54226953931549</v>
       </c>
       <c r="O8" t="n">
-        <v>5.154915703045439</v>
+        <v>5.151919015213213</v>
       </c>
       <c r="P8" t="n">
-        <v>341.0169377795723</v>
+        <v>341.011060957487</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39397,28 +39449,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03602660453426226</v>
+        <v>0.03633137751474909</v>
       </c>
       <c r="J9" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K9" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003259476867084721</v>
+        <v>0.003324680332309482</v>
       </c>
       <c r="M9" t="n">
-        <v>3.512674507045257</v>
+        <v>3.509815647652931</v>
       </c>
       <c r="N9" t="n">
-        <v>20.92158082086139</v>
+        <v>20.89465720446893</v>
       </c>
       <c r="O9" t="n">
-        <v>4.574011458322048</v>
+        <v>4.571067403185927</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8692569676454</v>
+        <v>343.8660534260682</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39475,28 +39527,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0498829778940033</v>
+        <v>0.05004115621447674</v>
       </c>
       <c r="J10" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K10" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009620664864685158</v>
+        <v>0.009710643835727617</v>
       </c>
       <c r="M10" t="n">
-        <v>2.967367381503043</v>
+        <v>2.964060515951521</v>
       </c>
       <c r="N10" t="n">
-        <v>13.50252056306426</v>
+        <v>13.48455032800239</v>
       </c>
       <c r="O10" t="n">
-        <v>3.674577603353107</v>
+        <v>3.672131578252934</v>
       </c>
       <c r="P10" t="n">
-        <v>349.025563074332</v>
+        <v>349.0239004242327</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39553,28 +39605,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003476701794771195</v>
+        <v>0.003644587515862371</v>
       </c>
       <c r="J11" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K11" t="n">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="L11" t="n">
-        <v>4.998767077968314e-05</v>
+        <v>5.510009950526751e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.745286093383207</v>
+        <v>2.742385876727015</v>
       </c>
       <c r="N11" t="n">
-        <v>12.74570588375998</v>
+        <v>12.72882056856637</v>
       </c>
       <c r="O11" t="n">
-        <v>3.570112867089776</v>
+        <v>3.567747268034322</v>
       </c>
       <c r="P11" t="n">
-        <v>357.5094396560803</v>
+        <v>357.5076749691751</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39612,7 +39664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L734"/>
+  <dimension ref="A1:L735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85123,6 +85175,68 @@
         </is>
       </c>
     </row>
+    <row r="735">
+      <c r="A735" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>-39.857702318273546,176.9856983958629</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>-39.85803545086662,176.98490740735582</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>-39.85845994145112,176.98418773459997</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>-39.85900046937095,176.98362333478315</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>-39.85949719076087,176.9829874715755</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>-39.86003058344369,176.98240622709488</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>-39.86060697470588,176.98190764893835</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>-39.861216343304896,176.98147485625887</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>-39.86185144405117,176.98111205748913</t>
+        </is>
+      </c>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>-39.862494921652775,176.98078814950986</t>
+        </is>
+      </c>
+      <c r="L735" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L735"/>
+  <dimension ref="A1:L738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31318,6 +31318,132 @@
       <c r="L735" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:30+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>340.25</v>
+      </c>
+      <c r="C736" t="n">
+        <v>333.61</v>
+      </c>
+      <c r="D736" t="n">
+        <v>340.83</v>
+      </c>
+      <c r="E736" t="n">
+        <v>357.67</v>
+      </c>
+      <c r="F736" t="n">
+        <v>345.82</v>
+      </c>
+      <c r="G736" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="H736" t="n">
+        <v>341.27</v>
+      </c>
+      <c r="I736" t="n">
+        <v>346.56</v>
+      </c>
+      <c r="J736" t="n">
+        <v>350.12</v>
+      </c>
+      <c r="K736" t="n">
+        <v>357.67</v>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>340.66</v>
+      </c>
+      <c r="C737" t="n">
+        <v>333.73</v>
+      </c>
+      <c r="D737" t="n">
+        <v>340.99</v>
+      </c>
+      <c r="E737" t="n">
+        <v>358.07</v>
+      </c>
+      <c r="F737" t="n">
+        <v>346.47</v>
+      </c>
+      <c r="G737" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="H737" t="n">
+        <v>341.44</v>
+      </c>
+      <c r="I737" t="n">
+        <v>346.74</v>
+      </c>
+      <c r="J737" t="n">
+        <v>350.44</v>
+      </c>
+      <c r="K737" t="n">
+        <v>358.53</v>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:51+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>340.02</v>
+      </c>
+      <c r="C738" t="n">
+        <v>333.89</v>
+      </c>
+      <c r="D738" t="n">
+        <v>342.44</v>
+      </c>
+      <c r="E738" t="n">
+        <v>358.76</v>
+      </c>
+      <c r="F738" t="n">
+        <v>347.77</v>
+      </c>
+      <c r="G738" t="n">
+        <v>340.57</v>
+      </c>
+      <c r="H738" t="n">
+        <v>342.27</v>
+      </c>
+      <c r="I738" t="n">
+        <v>346.98</v>
+      </c>
+      <c r="J738" t="n">
+        <v>350.7</v>
+      </c>
+      <c r="K738" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -31332,7 +31458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38735,6 +38861,36 @@
       </c>
       <c r="B740" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -38903,28 +39059,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4836320572353706</v>
+        <v>-0.4750917745298812</v>
       </c>
       <c r="J2" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K2" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L2" t="n">
-        <v>0.141421292308189</v>
+        <v>0.1375963283737101</v>
       </c>
       <c r="M2" t="n">
-        <v>7.134915868652906</v>
+        <v>7.145674868222565</v>
       </c>
       <c r="N2" t="n">
-        <v>74.98306423417993</v>
+        <v>75.09233006336174</v>
       </c>
       <c r="O2" t="n">
-        <v>8.659276195744072</v>
+        <v>8.66558307694074</v>
       </c>
       <c r="P2" t="n">
-        <v>342.89855804581</v>
+        <v>342.8085404706384</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38981,28 +39137,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1964558732308434</v>
+        <v>-0.1957079904516611</v>
       </c>
       <c r="J3" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K3" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0936724552865571</v>
+        <v>0.09380080218192866</v>
       </c>
       <c r="M3" t="n">
-        <v>3.731278100724995</v>
+        <v>3.71951932593668</v>
       </c>
       <c r="N3" t="n">
-        <v>19.71837041774949</v>
+        <v>19.64133677769414</v>
       </c>
       <c r="O3" t="n">
-        <v>4.440537176710662</v>
+        <v>4.43185477849784</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0313644365659</v>
+        <v>338.0234806036273</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39059,28 +39215,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1672034102703393</v>
+        <v>-0.1641359129244225</v>
       </c>
       <c r="J4" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K4" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03781984019277873</v>
+        <v>0.03677102829246015</v>
       </c>
       <c r="M4" t="n">
-        <v>5.080915791375064</v>
+        <v>5.074147568233504</v>
       </c>
       <c r="N4" t="n">
-        <v>37.55732754334676</v>
+        <v>37.46000215207238</v>
       </c>
       <c r="O4" t="n">
-        <v>6.128403343722307</v>
+        <v>6.120457675049504</v>
       </c>
       <c r="P4" t="n">
-        <v>342.1754688232541</v>
+        <v>342.1431313595293</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39137,28 +39293,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06886923962471884</v>
+        <v>-0.06591115441013154</v>
       </c>
       <c r="J5" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K5" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01266013926437759</v>
+        <v>0.01168554109951214</v>
       </c>
       <c r="M5" t="n">
-        <v>3.448016295965834</v>
+        <v>3.44894859455658</v>
       </c>
       <c r="N5" t="n">
-        <v>19.53198918841714</v>
+        <v>19.50297950953152</v>
       </c>
       <c r="O5" t="n">
-        <v>4.41950101124744</v>
+        <v>4.416217783299587</v>
       </c>
       <c r="P5" t="n">
-        <v>356.464818056972</v>
+        <v>356.4336354129227</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39215,28 +39371,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2269348268136334</v>
+        <v>-0.2249396486555602</v>
       </c>
       <c r="J6" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K6" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08353452317434107</v>
+        <v>0.08283227608034016</v>
       </c>
       <c r="M6" t="n">
-        <v>4.264110285686952</v>
+        <v>4.258375555655975</v>
       </c>
       <c r="N6" t="n">
-        <v>29.83459346470155</v>
+        <v>29.73842741196329</v>
       </c>
       <c r="O6" t="n">
-        <v>5.462105222778261</v>
+        <v>5.453295096724849</v>
       </c>
       <c r="P6" t="n">
-        <v>350.2962841869776</v>
+        <v>350.2752484796009</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39293,28 +39449,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2932247772267718</v>
+        <v>-0.29029644237995</v>
       </c>
       <c r="J7" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K7" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1311807322398136</v>
+        <v>0.1297737254477423</v>
       </c>
       <c r="M7" t="n">
-        <v>4.245272261428267</v>
+        <v>4.242272598379828</v>
       </c>
       <c r="N7" t="n">
-        <v>30.0696542506283</v>
+        <v>29.99615939693672</v>
       </c>
       <c r="O7" t="n">
-        <v>5.483580422554984</v>
+        <v>5.476874966341364</v>
       </c>
       <c r="P7" t="n">
-        <v>344.5217392075239</v>
+        <v>344.4908716724227</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39371,28 +39527,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1370901253732194</v>
+        <v>-0.1335057364676853</v>
       </c>
       <c r="J8" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K8" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03604129867650385</v>
+        <v>0.03446119150052596</v>
       </c>
       <c r="M8" t="n">
-        <v>4.020951806549372</v>
+        <v>4.024596750645698</v>
       </c>
       <c r="N8" t="n">
-        <v>26.54226953931549</v>
+        <v>26.50794769872763</v>
       </c>
       <c r="O8" t="n">
-        <v>5.151919015213213</v>
+        <v>5.148586961364024</v>
       </c>
       <c r="P8" t="n">
-        <v>341.011060957487</v>
+        <v>340.9732770291158</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39449,28 +39605,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03633137751474909</v>
+        <v>0.03796210703481267</v>
       </c>
       <c r="J9" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K9" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003324680332309482</v>
+        <v>0.003659853737196794</v>
       </c>
       <c r="M9" t="n">
-        <v>3.509815647652931</v>
+        <v>3.505740481658183</v>
       </c>
       <c r="N9" t="n">
-        <v>20.89465720446893</v>
+        <v>20.82482331255627</v>
       </c>
       <c r="O9" t="n">
-        <v>4.571067403185927</v>
+        <v>4.56342232458889</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8660534260682</v>
+        <v>343.8488636179972</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39527,28 +39683,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05004115621447674</v>
+        <v>0.05010594239625431</v>
       </c>
       <c r="J10" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K10" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009710643835727617</v>
+        <v>0.009825481203754483</v>
       </c>
       <c r="M10" t="n">
-        <v>2.964060515951521</v>
+        <v>2.952900962195184</v>
       </c>
       <c r="N10" t="n">
-        <v>13.48455032800239</v>
+        <v>13.4299127920119</v>
       </c>
       <c r="O10" t="n">
-        <v>3.672131578252934</v>
+        <v>3.66468454195063</v>
       </c>
       <c r="P10" t="n">
-        <v>349.0239004242327</v>
+        <v>349.0232158859805</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39605,28 +39761,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003644587515862371</v>
+        <v>0.004410572117351244</v>
       </c>
       <c r="J11" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="K11" t="n">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="L11" t="n">
-        <v>5.510009950526751e-05</v>
+        <v>8.141336042122305e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.742385876727015</v>
+        <v>2.735026404493994</v>
       </c>
       <c r="N11" t="n">
-        <v>12.72882056856637</v>
+        <v>12.6822298960271</v>
       </c>
       <c r="O11" t="n">
-        <v>3.567747268034322</v>
+        <v>3.561211857784804</v>
       </c>
       <c r="P11" t="n">
-        <v>357.5076749691751</v>
+        <v>357.4995963500157</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39664,7 +39820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L735"/>
+  <dimension ref="A1:L738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85237,6 +85393,192 @@
         </is>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-01 22:00:30+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>-39.85770951698789,176.98570479776077</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>-39.85803277916676,176.98490503140118</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>-39.85846172500867,176.9841895128769</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>-39.859001601096736,176.98362499721367</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>-39.85949863929113,176.98299028751458</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>-39.86003306424816,176.9824112359195</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>-39.86061590848778,176.98192642358933</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>-39.86121918696925,176.98148162064757</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>-39.861848454812844,176.98110381847457</t>
+        </is>
+      </c>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>-39.86249291834199,176.98078253428602</t>
+        </is>
+      </c>
+      <c r="L736" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-09 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>-39.8577125597433,176.985707503718</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>-39.85803366973339,176.98490582338604</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>-39.85846286648546,176.9841906509742</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>-39.85900398367724,176.98362849706757</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>-39.859501885996615,176.98299659910265</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>-39.86003413439904,176.98241339658904</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>-39.86061671205532,176.9819281123148</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>-39.861219962514,176.98148346548098</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>-39.861849681167094,176.981107198583</t>
+        </is>
+      </c>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>-39.86249616899708,176.98079164578147</t>
+        </is>
+      </c>
+      <c r="L737" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-18 21:54:51+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>-39.85770781007628,176.98570327978487</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>-39.858034857155545,176.9849068793659</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>-39.85847321111838,176.98420096498262</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>-39.859008093628354,176.98363453431608</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>-39.85950837940644,176.98300922228046</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>-39.86003573962526,176.98241663759347</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>-39.86062063535518,176.98193635726903</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>-39.861220996573614,176.98148592525885</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>-39.86185067757985,176.9811099449212</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>-39.86249923065991,176.98080022753953</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L738"/>
+  <dimension ref="A1:L739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31442,6 +31442,48 @@
         <v>359.34</v>
       </c>
       <c r="L738" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>341.53</v>
+      </c>
+      <c r="C739" t="n">
+        <v>334.92</v>
+      </c>
+      <c r="D739" t="n">
+        <v>343.29</v>
+      </c>
+      <c r="E739" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="F739" t="n">
+        <v>349.11</v>
+      </c>
+      <c r="G739" t="n">
+        <v>341.36</v>
+      </c>
+      <c r="H739" t="n">
+        <v>342.18</v>
+      </c>
+      <c r="I739" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="J739" t="n">
+        <v>350.91</v>
+      </c>
+      <c r="K739" t="n">
+        <v>359.46</v>
+      </c>
+      <c r="L739" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31458,7 +31500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B743"/>
+  <dimension ref="A1:B744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38891,6 +38933,16 @@
       </c>
       <c r="B743" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
@@ -39059,28 +39111,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4750917745298812</v>
+        <v>-0.4719191095037843</v>
       </c>
       <c r="J2" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K2" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1375963283737101</v>
+        <v>0.1361111916733031</v>
       </c>
       <c r="M2" t="n">
-        <v>7.145674868222565</v>
+        <v>7.150724643112117</v>
       </c>
       <c r="N2" t="n">
-        <v>75.09233006336174</v>
+        <v>75.16219474714056</v>
       </c>
       <c r="O2" t="n">
-        <v>8.66558307694074</v>
+        <v>8.669613298592997</v>
       </c>
       <c r="P2" t="n">
-        <v>342.8085404706384</v>
+        <v>342.7749787723355</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39137,28 +39189,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1957079904516611</v>
+        <v>-0.195126943189546</v>
       </c>
       <c r="J3" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K3" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09380080218192866</v>
+        <v>0.09353540762308621</v>
       </c>
       <c r="M3" t="n">
-        <v>3.71951932593668</v>
+        <v>3.717119301625075</v>
       </c>
       <c r="N3" t="n">
-        <v>19.64133677769414</v>
+        <v>19.62047864576345</v>
       </c>
       <c r="O3" t="n">
-        <v>4.43185477849784</v>
+        <v>4.429500947709962</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0234806036273</v>
+        <v>338.0173340571906</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39215,28 +39267,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1641359129244225</v>
+        <v>-0.1625935902823793</v>
       </c>
       <c r="J4" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K4" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03677102829246015</v>
+        <v>0.03617879787316758</v>
       </c>
       <c r="M4" t="n">
-        <v>5.074147568233504</v>
+        <v>5.07425880589803</v>
       </c>
       <c r="N4" t="n">
-        <v>37.46000215207238</v>
+        <v>37.44979973402262</v>
       </c>
       <c r="O4" t="n">
-        <v>6.120457675049504</v>
+        <v>6.119624149735229</v>
       </c>
       <c r="P4" t="n">
-        <v>342.1431313595293</v>
+        <v>342.1268160641003</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39293,28 +39345,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06591115441013154</v>
+        <v>-0.06459901258959064</v>
       </c>
       <c r="J5" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K5" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01168554109951214</v>
+        <v>0.01124794862184064</v>
       </c>
       <c r="M5" t="n">
-        <v>3.44894859455658</v>
+        <v>3.450891384486725</v>
       </c>
       <c r="N5" t="n">
-        <v>19.50297950953152</v>
+        <v>19.5059069184746</v>
       </c>
       <c r="O5" t="n">
-        <v>4.416217783299587</v>
+        <v>4.416549209334659</v>
       </c>
       <c r="P5" t="n">
-        <v>356.4336354129227</v>
+        <v>356.4197550607427</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39371,28 +39423,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2249396486555602</v>
+        <v>-0.2235961804299759</v>
       </c>
       <c r="J6" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K6" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08283227608034016</v>
+        <v>0.08208306401083965</v>
       </c>
       <c r="M6" t="n">
-        <v>4.258375555655975</v>
+        <v>4.260371199449071</v>
       </c>
       <c r="N6" t="n">
-        <v>29.73842741196329</v>
+        <v>29.72890400127762</v>
       </c>
       <c r="O6" t="n">
-        <v>5.453295096724849</v>
+        <v>5.452421847333313</v>
       </c>
       <c r="P6" t="n">
-        <v>350.2752484796009</v>
+        <v>350.2610367443892</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39449,28 +39501,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.29029644237995</v>
+        <v>-0.2890188339340818</v>
       </c>
       <c r="J7" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K7" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1297737254477423</v>
+        <v>0.1290261289468281</v>
       </c>
       <c r="M7" t="n">
-        <v>4.242272598379828</v>
+        <v>4.242725326867826</v>
       </c>
       <c r="N7" t="n">
-        <v>29.99615939693672</v>
+        <v>29.98334362997412</v>
       </c>
       <c r="O7" t="n">
-        <v>5.476874966341364</v>
+        <v>5.475704852343132</v>
       </c>
       <c r="P7" t="n">
-        <v>344.4908716724227</v>
+        <v>344.4773566278603</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39527,28 +39579,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1335057364676853</v>
+        <v>-0.1321729753255801</v>
       </c>
       <c r="J8" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K8" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03446119150052596</v>
+        <v>0.03386414136414484</v>
       </c>
       <c r="M8" t="n">
-        <v>4.024596750645698</v>
+        <v>4.026578663364655</v>
       </c>
       <c r="N8" t="n">
-        <v>26.50794769872763</v>
+        <v>26.50231308818084</v>
       </c>
       <c r="O8" t="n">
-        <v>5.148586961364024</v>
+        <v>5.148039732575968</v>
       </c>
       <c r="P8" t="n">
-        <v>340.9732770291158</v>
+        <v>340.9591785576437</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39605,28 +39657,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03796210703481267</v>
+        <v>0.03843032610971857</v>
       </c>
       <c r="J9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003659853737196794</v>
+        <v>0.003761329242973677</v>
       </c>
       <c r="M9" t="n">
-        <v>3.505740481658183</v>
+        <v>3.503898273394887</v>
       </c>
       <c r="N9" t="n">
-        <v>20.82482331255627</v>
+        <v>20.80034311727683</v>
       </c>
       <c r="O9" t="n">
-        <v>4.56342232458889</v>
+        <v>4.560739316961323</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8488636179972</v>
+        <v>343.8439106124948</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39683,28 +39735,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05010594239625431</v>
+        <v>0.05026410513224615</v>
       </c>
       <c r="J10" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K10" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009825481203754483</v>
+        <v>0.009917212197381065</v>
       </c>
       <c r="M10" t="n">
-        <v>2.952900962195184</v>
+        <v>2.949627361314834</v>
       </c>
       <c r="N10" t="n">
-        <v>13.4299127920119</v>
+        <v>13.41214157638576</v>
       </c>
       <c r="O10" t="n">
-        <v>3.66468454195063</v>
+        <v>3.662259081002566</v>
       </c>
       <c r="P10" t="n">
-        <v>349.0232158859805</v>
+        <v>349.0215427783614</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39761,28 +39813,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004410572117351244</v>
+        <v>0.004929426170530517</v>
       </c>
       <c r="J11" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K11" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L11" t="n">
-        <v>8.141336042122305e-05</v>
+        <v>0.0001019728716729063</v>
       </c>
       <c r="M11" t="n">
-        <v>2.735026404493994</v>
+        <v>2.733888061468634</v>
       </c>
       <c r="N11" t="n">
-        <v>12.6822298960271</v>
+        <v>12.66963516094845</v>
       </c>
       <c r="O11" t="n">
-        <v>3.561211857784804</v>
+        <v>3.559443097023529</v>
       </c>
       <c r="P11" t="n">
-        <v>357.4995963500157</v>
+        <v>357.4941077078008</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39820,7 +39872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L738"/>
+  <dimension ref="A1:L739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85579,6 +85631,68 @@
         </is>
       </c>
     </row>
+    <row r="739">
+      <c r="A739" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:33+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>-39.85771901632163,176.98571324562812</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>-39.8580425011854,176.98491367723705</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>-39.85847927521303,176.98420701112698</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>-39.85901166749858,176.98363978409802</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>-39.85951507261194,176.9830222338662</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>-39.860039582439185,176.9824243963623</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>-39.86062020993716,176.9819354632378</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>-39.861219014625966,176.98148121068462</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>-39.861851482374725,176.98111216311753</t>
+        </is>
+      </c>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>-39.86249968423952,176.9808014989112</t>
+        </is>
+      </c>
+      <c r="L739" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L739"/>
+  <dimension ref="A1:L741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31484,6 +31484,90 @@
         <v>359.46</v>
       </c>
       <c r="L739" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:43+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>343.72</v>
+      </c>
+      <c r="C740" t="n">
+        <v>335.89</v>
+      </c>
+      <c r="D740" t="n">
+        <v>344.43</v>
+      </c>
+      <c r="E740" t="n">
+        <v>360.41</v>
+      </c>
+      <c r="F740" t="n">
+        <v>350.26</v>
+      </c>
+      <c r="G740" t="n">
+        <v>341.61</v>
+      </c>
+      <c r="H740" t="n">
+        <v>342.61</v>
+      </c>
+      <c r="I740" t="n">
+        <v>346.96</v>
+      </c>
+      <c r="J740" t="n">
+        <v>351.57</v>
+      </c>
+      <c r="K740" t="n">
+        <v>360.96</v>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:36+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>343.72</v>
+      </c>
+      <c r="C741" t="n">
+        <v>336</v>
+      </c>
+      <c r="D741" t="n">
+        <v>344</v>
+      </c>
+      <c r="E741" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="F741" t="n">
+        <v>350.53</v>
+      </c>
+      <c r="G741" t="n">
+        <v>342.33</v>
+      </c>
+      <c r="H741" t="n">
+        <v>342.02</v>
+      </c>
+      <c r="I741" t="n">
+        <v>346.53</v>
+      </c>
+      <c r="J741" t="n">
+        <v>351.55</v>
+      </c>
+      <c r="K741" t="n">
+        <v>360.91</v>
+      </c>
+      <c r="L741" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31500,7 +31584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B744"/>
+  <dimension ref="A1:B746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38943,6 +39027,26 @@
       </c>
       <c r="B744" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -39111,28 +39215,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4719191095037843</v>
+        <v>-0.4643541137478685</v>
       </c>
       <c r="J2" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K2" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1361111916733031</v>
+        <v>0.132335067884762</v>
       </c>
       <c r="M2" t="n">
-        <v>7.150724643112117</v>
+        <v>7.166622936495012</v>
       </c>
       <c r="N2" t="n">
-        <v>75.16219474714056</v>
+        <v>75.44420945132315</v>
       </c>
       <c r="O2" t="n">
-        <v>8.669613298592997</v>
+        <v>8.685862619873927</v>
       </c>
       <c r="P2" t="n">
-        <v>342.7749787723355</v>
+        <v>342.6946573584856</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39189,28 +39293,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.195126943189546</v>
+        <v>-0.1933811149411111</v>
       </c>
       <c r="J3" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K3" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09353540762308621</v>
+        <v>0.09243734449676477</v>
       </c>
       <c r="M3" t="n">
-        <v>3.717119301625075</v>
+        <v>3.715005160700017</v>
       </c>
       <c r="N3" t="n">
-        <v>19.62047864576345</v>
+        <v>19.59329569793752</v>
       </c>
       <c r="O3" t="n">
-        <v>4.429500947709962</v>
+        <v>4.426431485738543</v>
       </c>
       <c r="P3" t="n">
-        <v>338.0173340571906</v>
+        <v>337.9987974191904</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39267,28 +39371,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1625935902823793</v>
+        <v>-0.1589954467810496</v>
       </c>
       <c r="J4" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K4" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03617879787316758</v>
+        <v>0.03476193868481459</v>
       </c>
       <c r="M4" t="n">
-        <v>5.07425880589803</v>
+        <v>5.076785534917665</v>
       </c>
       <c r="N4" t="n">
-        <v>37.44979973402262</v>
+        <v>37.45847056249252</v>
       </c>
       <c r="O4" t="n">
-        <v>6.119624149735229</v>
+        <v>6.120332553259874</v>
       </c>
       <c r="P4" t="n">
-        <v>342.1268160641003</v>
+        <v>342.0886138817469</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39345,28 +39449,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06459901258959064</v>
+        <v>-0.06143843733361894</v>
       </c>
       <c r="J5" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K5" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01124794862184064</v>
+        <v>0.01020465239261648</v>
       </c>
       <c r="M5" t="n">
-        <v>3.450891384486725</v>
+        <v>3.457508736354884</v>
       </c>
       <c r="N5" t="n">
-        <v>19.5059069184746</v>
+        <v>19.53789319801708</v>
       </c>
       <c r="O5" t="n">
-        <v>4.416549209334659</v>
+        <v>4.420168910575373</v>
       </c>
       <c r="P5" t="n">
-        <v>356.4197550607427</v>
+        <v>356.3861980694139</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39423,28 +39527,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2235961804299759</v>
+        <v>-0.220187306138161</v>
       </c>
       <c r="J6" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K6" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08208306401083965</v>
+        <v>0.08001488063589512</v>
       </c>
       <c r="M6" t="n">
-        <v>4.260371199449071</v>
+        <v>4.268394941289364</v>
       </c>
       <c r="N6" t="n">
-        <v>29.72890400127762</v>
+        <v>29.74711237382823</v>
       </c>
       <c r="O6" t="n">
-        <v>5.452421847333313</v>
+        <v>5.454091342637033</v>
       </c>
       <c r="P6" t="n">
-        <v>350.2610367443892</v>
+        <v>350.2248422573171</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39501,28 +39605,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2890188339340818</v>
+        <v>-0.2861196410152964</v>
       </c>
       <c r="J7" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K7" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1290261289468281</v>
+        <v>0.1272076241811023</v>
       </c>
       <c r="M7" t="n">
-        <v>4.242725326867826</v>
+        <v>4.245318673669147</v>
       </c>
       <c r="N7" t="n">
-        <v>29.98334362997412</v>
+        <v>29.97390745135438</v>
       </c>
       <c r="O7" t="n">
-        <v>5.475704852343132</v>
+        <v>5.474843143995486</v>
       </c>
       <c r="P7" t="n">
-        <v>344.4773566278603</v>
+        <v>344.446572482289</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39579,28 +39683,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1321729753255801</v>
+        <v>-0.1294419693515703</v>
       </c>
       <c r="J8" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K8" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03386414136414484</v>
+        <v>0.03264642345916013</v>
       </c>
       <c r="M8" t="n">
-        <v>4.026578663364655</v>
+        <v>4.030831813296931</v>
       </c>
       <c r="N8" t="n">
-        <v>26.50231308818084</v>
+        <v>26.49415497224047</v>
       </c>
       <c r="O8" t="n">
-        <v>5.148039732575968</v>
+        <v>5.147247319902208</v>
       </c>
       <c r="P8" t="n">
-        <v>340.9591785576437</v>
+        <v>340.9301836405077</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39657,28 +39761,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03843032610971857</v>
+        <v>0.03948984436818157</v>
       </c>
       <c r="J9" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K9" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003761329242973677</v>
+        <v>0.003993797602840243</v>
       </c>
       <c r="M9" t="n">
-        <v>3.503898273394887</v>
+        <v>3.500974068675546</v>
       </c>
       <c r="N9" t="n">
-        <v>20.80034311727683</v>
+        <v>20.75377251015122</v>
       </c>
       <c r="O9" t="n">
-        <v>4.560739316961323</v>
+        <v>4.555630857537869</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8439106124948</v>
+        <v>343.8326623249757</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39735,28 +39839,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05026410513224615</v>
+        <v>0.05094195994969229</v>
       </c>
       <c r="J10" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K10" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L10" t="n">
-        <v>0.009917212197381065</v>
+        <v>0.01024425339001112</v>
       </c>
       <c r="M10" t="n">
-        <v>2.949627361314834</v>
+        <v>2.944738154862329</v>
       </c>
       <c r="N10" t="n">
-        <v>13.41214157638576</v>
+        <v>13.37978813929149</v>
       </c>
       <c r="O10" t="n">
-        <v>3.662259081002566</v>
+        <v>3.657839271932473</v>
       </c>
       <c r="P10" t="n">
-        <v>349.0215427783614</v>
+        <v>349.014345699937</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39813,28 +39917,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004929426170530517</v>
+        <v>0.006790577557532092</v>
       </c>
       <c r="J11" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="K11" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001019728716729063</v>
+        <v>0.000194259500630678</v>
       </c>
       <c r="M11" t="n">
-        <v>2.733888061468634</v>
+        <v>2.735649903867495</v>
       </c>
       <c r="N11" t="n">
-        <v>12.66963516094845</v>
+        <v>12.66476111054478</v>
       </c>
       <c r="O11" t="n">
-        <v>3.559443097023529</v>
+        <v>3.558758366417251</v>
       </c>
       <c r="P11" t="n">
-        <v>357.4941077078008</v>
+        <v>357.4743470844026</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39872,7 +39976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L739"/>
+  <dimension ref="A1:L741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85693,6 +85797,130 @@
         </is>
       </c>
     </row>
+    <row r="740">
+      <c r="A740" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-04 21:54:43+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>-39.857735269086206,176.9857276994067</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>-39.85804969993152,176.98492007911716</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>-39.85848740823351,176.98421512007525</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>-39.859017921770864,176.98364897121766</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>-39.85952081677955,176.98303340052755</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>-39.860040798519435,176.98242685166906</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>-39.86062224248989,176.9819397347204</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>-39.86122091040198,176.98148572027736</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>-39.86185401172975,176.98111913459192</t>
+        </is>
+      </c>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>-39.86250535398352,176.98081739105788</t>
+        </is>
+      </c>
+      <c r="L740" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-20 21:54:36+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>-39.857735269086206,176.9857276994067</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>-39.85805051628414,176.98492080510366</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>-39.85848434051534,176.98421206143664</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>-39.85901696873894,176.9836475712755</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>-39.85952216541004,176.98303602226568</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>-39.8600443008302,176.98243392295302</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>-39.860619453638414,176.98193387384896</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>-39.8612190577118,176.98148131317535</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>-39.86185393508263,176.9811189233351</t>
+        </is>
+      </c>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>-39.8625051649921,176.98081686131962</t>
+        </is>
+      </c>
+      <c r="L741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L741"/>
+  <dimension ref="A1:L743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31568,6 +31568,90 @@
         <v>360.91</v>
       </c>
       <c r="L741" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:27+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>344.02</v>
+      </c>
+      <c r="C742" t="n">
+        <v>336.05</v>
+      </c>
+      <c r="D742" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="E742" t="n">
+        <v>360.92</v>
+      </c>
+      <c r="F742" t="n">
+        <v>352.26</v>
+      </c>
+      <c r="G742" t="n">
+        <v>344.44</v>
+      </c>
+      <c r="H742" t="n">
+        <v>342.87</v>
+      </c>
+      <c r="I742" t="n">
+        <v>346.43</v>
+      </c>
+      <c r="J742" t="n">
+        <v>352.21</v>
+      </c>
+      <c r="K742" t="n">
+        <v>361.54</v>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>344.53</v>
+      </c>
+      <c r="C743" t="n">
+        <v>336.29</v>
+      </c>
+      <c r="D743" t="n">
+        <v>344.47</v>
+      </c>
+      <c r="E743" t="n">
+        <v>360.87</v>
+      </c>
+      <c r="F743" t="n">
+        <v>352.89</v>
+      </c>
+      <c r="G743" t="n">
+        <v>345.46</v>
+      </c>
+      <c r="H743" t="n">
+        <v>342.88</v>
+      </c>
+      <c r="I743" t="n">
+        <v>346.53</v>
+      </c>
+      <c r="J743" t="n">
+        <v>351.94</v>
+      </c>
+      <c r="K743" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="L743" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31584,7 +31668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B746"/>
+  <dimension ref="A1:B748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39047,6 +39131,26 @@
       </c>
       <c r="B746" t="n">
         <v>0.51</v>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -39215,28 +39319,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4643541137478685</v>
+        <v>-0.4565501333698372</v>
       </c>
       <c r="J2" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K2" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L2" t="n">
-        <v>0.132335067884762</v>
+        <v>0.1284249097856757</v>
       </c>
       <c r="M2" t="n">
-        <v>7.166622936495012</v>
+        <v>7.183847231275743</v>
       </c>
       <c r="N2" t="n">
-        <v>75.44420945132315</v>
+        <v>75.75921268216626</v>
       </c>
       <c r="O2" t="n">
-        <v>8.685862619873927</v>
+        <v>8.703976831435517</v>
       </c>
       <c r="P2" t="n">
-        <v>342.6946573584856</v>
+        <v>342.6115809980853</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39293,28 +39397,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1933811149411111</v>
+        <v>-0.1915249869720543</v>
       </c>
       <c r="J3" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K3" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09243734449676477</v>
+        <v>0.09122675154793602</v>
       </c>
       <c r="M3" t="n">
-        <v>3.715005160700017</v>
+        <v>3.713357223732543</v>
       </c>
       <c r="N3" t="n">
-        <v>19.59329569793752</v>
+        <v>19.56983532125239</v>
       </c>
       <c r="O3" t="n">
-        <v>4.426431485738543</v>
+        <v>4.42378065926108</v>
       </c>
       <c r="P3" t="n">
-        <v>337.9987974191904</v>
+        <v>337.9790379242814</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39371,28 +39475,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1589954467810496</v>
+        <v>-0.1553662935713178</v>
       </c>
       <c r="J4" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K4" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03476193868481459</v>
+        <v>0.03335080034615356</v>
       </c>
       <c r="M4" t="n">
-        <v>5.076785534917665</v>
+        <v>5.079454366324732</v>
       </c>
       <c r="N4" t="n">
-        <v>37.45847056249252</v>
+        <v>37.46961323611622</v>
       </c>
       <c r="O4" t="n">
-        <v>6.120332553259874</v>
+        <v>6.12124278526152</v>
       </c>
       <c r="P4" t="n">
-        <v>342.0886138817469</v>
+        <v>342.0499800889781</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39449,28 +39553,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.06143843733361894</v>
+        <v>-0.05799790207686966</v>
       </c>
       <c r="J5" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K5" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01020465239261648</v>
+        <v>0.009113946887972846</v>
       </c>
       <c r="M5" t="n">
-        <v>3.457508736354884</v>
+        <v>3.465603741787665</v>
       </c>
       <c r="N5" t="n">
-        <v>19.53789319801708</v>
+        <v>19.58595514396578</v>
       </c>
       <c r="O5" t="n">
-        <v>4.420168910575373</v>
+        <v>4.42560223517272</v>
       </c>
       <c r="P5" t="n">
-        <v>356.3861980694139</v>
+        <v>356.3495729598924</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39527,28 +39631,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.220187306138161</v>
+        <v>-0.2155896065209582</v>
       </c>
       <c r="J6" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K6" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08001488063589512</v>
+        <v>0.07697843634159096</v>
       </c>
       <c r="M6" t="n">
-        <v>4.268394941289364</v>
+        <v>4.283495303825168</v>
       </c>
       <c r="N6" t="n">
-        <v>29.74711237382823</v>
+        <v>29.84704678463998</v>
       </c>
       <c r="O6" t="n">
-        <v>5.454091342637033</v>
+        <v>5.46324507821496</v>
       </c>
       <c r="P6" t="n">
-        <v>350.2248422573171</v>
+        <v>350.1758971703543</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39605,28 +39709,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2861196410152964</v>
+        <v>-0.2815748765461854</v>
       </c>
       <c r="J7" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K7" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1272076241811023</v>
+        <v>0.1237367422452729</v>
       </c>
       <c r="M7" t="n">
-        <v>4.245318673669147</v>
+        <v>4.256027241587218</v>
       </c>
       <c r="N7" t="n">
-        <v>29.97390745135438</v>
+        <v>30.06953370136938</v>
       </c>
       <c r="O7" t="n">
-        <v>5.474843143995486</v>
+        <v>5.483569430705641</v>
       </c>
       <c r="P7" t="n">
-        <v>344.446572482289</v>
+        <v>344.3981899347325</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39683,28 +39787,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1294419693515703</v>
+        <v>-0.1264236289668675</v>
       </c>
       <c r="J8" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K8" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03264642345916013</v>
+        <v>0.03128982863644847</v>
       </c>
       <c r="M8" t="n">
-        <v>4.030831813296931</v>
+        <v>4.03657543304026</v>
       </c>
       <c r="N8" t="n">
-        <v>26.49415497224047</v>
+        <v>26.50026059396843</v>
       </c>
       <c r="O8" t="n">
-        <v>5.147247319902208</v>
+        <v>5.147840381555009</v>
       </c>
       <c r="P8" t="n">
-        <v>340.9301836405077</v>
+        <v>340.898052733855</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39761,28 +39865,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03948984436818157</v>
+        <v>0.0403859913505602</v>
       </c>
       <c r="J9" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K9" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003993797602840243</v>
+        <v>0.004201145604202927</v>
       </c>
       <c r="M9" t="n">
-        <v>3.500974068675546</v>
+        <v>3.497053478731873</v>
       </c>
       <c r="N9" t="n">
-        <v>20.75377251015122</v>
+        <v>20.70467171931783</v>
       </c>
       <c r="O9" t="n">
-        <v>4.555630857537869</v>
+        <v>4.550238644216129</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8326623249757</v>
+        <v>343.8231223975054</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39839,28 +39943,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05094195994969229</v>
+        <v>0.05189888569451694</v>
       </c>
       <c r="J10" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K10" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01024425339001112</v>
+        <v>0.0106885733898473</v>
       </c>
       <c r="M10" t="n">
-        <v>2.944738154862329</v>
+        <v>2.941199041489277</v>
       </c>
       <c r="N10" t="n">
-        <v>13.37978813929149</v>
+        <v>13.35156925716607</v>
       </c>
       <c r="O10" t="n">
-        <v>3.657839271932473</v>
+        <v>3.653979920191964</v>
       </c>
       <c r="P10" t="n">
-        <v>349.014345699937</v>
+        <v>349.0041597056809</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39917,28 +40021,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.006790577557532092</v>
+        <v>0.008812206262603919</v>
       </c>
       <c r="J11" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K11" t="n">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="L11" t="n">
-        <v>0.000194259500630678</v>
+        <v>0.0003282487896348885</v>
       </c>
       <c r="M11" t="n">
-        <v>2.735649903867495</v>
+        <v>2.738315799592853</v>
       </c>
       <c r="N11" t="n">
-        <v>12.66476111054478</v>
+        <v>12.66562305902352</v>
       </c>
       <c r="O11" t="n">
-        <v>3.558758366417251</v>
+        <v>3.55887946677371</v>
       </c>
       <c r="P11" t="n">
-        <v>357.4743470844026</v>
+        <v>357.4528278108963</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39976,7 +40080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L741"/>
+  <dimension ref="A1:L743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85921,6 +86025,130 @@
         </is>
       </c>
     </row>
+    <row r="742">
+      <c r="A742" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-28 21:54:27+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>-39.857737495492145,176.98572967937693</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>-39.858050887353514,176.9849211350975</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>-39.85848576736101,176.9842134840592</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>-39.85902095955996,176.98365343353353</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>-39.85953080663348,176.9830528208125</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>-39.86005456454375,176.9824546457475</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>-39.860623471475186,176.9819423174775</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>-39.86121862685357,176.98148028826796</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>-39.86185646443722,176.98112589481</t>
+        </is>
+      </c>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>-39.862507546283915,176.98082353602194</t>
+        </is>
+      </c>
+      <c r="L742" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:37+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>-39.85774128038216,176.98573304532658</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>-39.85805266848648,176.9849227190681</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>-39.85848769360264,176.98421540459978</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>-39.85902066173752,176.98365299605155</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>-39.85953395343674,176.9830589382034</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>-39.860059526147936,176.98246466340387</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>-39.86062351874384,176.9819424168143</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>-39.8612190577118,176.98148131317535</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>-39.86185542970132,176.98112304284294</t>
+        </is>
+      </c>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>-39.86250542958009,176.9808176029532</t>
+        </is>
+      </c>
+      <c r="L743" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L743"/>
+  <dimension ref="A1:L747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31652,6 +31652,174 @@
         <v>360.98</v>
       </c>
       <c r="L743" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>341.9</v>
+      </c>
+      <c r="C744" t="n">
+        <v>334.67</v>
+      </c>
+      <c r="D744" t="n">
+        <v>343.24</v>
+      </c>
+      <c r="E744" t="n">
+        <v>360.27</v>
+      </c>
+      <c r="F744" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="G744" t="n">
+        <v>345.16</v>
+      </c>
+      <c r="H744" t="n">
+        <v>340.9</v>
+      </c>
+      <c r="I744" t="n">
+        <v>344.95</v>
+      </c>
+      <c r="J744" t="n">
+        <v>351.52</v>
+      </c>
+      <c r="K744" t="n">
+        <v>359.72</v>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>341.41</v>
+      </c>
+      <c r="C745" t="n">
+        <v>334.34</v>
+      </c>
+      <c r="D745" t="n">
+        <v>343.41</v>
+      </c>
+      <c r="E745" t="n">
+        <v>359.78</v>
+      </c>
+      <c r="F745" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="G745" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="H745" t="n">
+        <v>338.95</v>
+      </c>
+      <c r="I745" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="J745" t="n">
+        <v>351.17</v>
+      </c>
+      <c r="K745" t="n">
+        <v>358.87</v>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>340.42</v>
+      </c>
+      <c r="C746" t="n">
+        <v>333.57</v>
+      </c>
+      <c r="D746" t="n">
+        <v>342.56</v>
+      </c>
+      <c r="E746" t="n">
+        <v>359.14</v>
+      </c>
+      <c r="F746" t="n">
+        <v>351.58</v>
+      </c>
+      <c r="G746" t="n">
+        <v>342.95</v>
+      </c>
+      <c r="H746" t="n">
+        <v>337.11</v>
+      </c>
+      <c r="I746" t="n">
+        <v>343.48</v>
+      </c>
+      <c r="J746" t="n">
+        <v>351.25</v>
+      </c>
+      <c r="K746" t="n">
+        <v>358.77</v>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="n">
+        <v>339.76</v>
+      </c>
+      <c r="C747" t="n">
+        <v>333.16</v>
+      </c>
+      <c r="D747" t="n">
+        <v>342.21</v>
+      </c>
+      <c r="E747" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="F747" t="n">
+        <v>351.46</v>
+      </c>
+      <c r="G747" t="n">
+        <v>342.83</v>
+      </c>
+      <c r="H747" t="n">
+        <v>336.48</v>
+      </c>
+      <c r="I747" t="n">
+        <v>343.14</v>
+      </c>
+      <c r="J747" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="K747" t="n">
+        <v>359.62</v>
+      </c>
+      <c r="L747" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -31668,7 +31836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B748"/>
+  <dimension ref="A1:B752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39151,6 +39319,46 @@
       </c>
       <c r="B748" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>
@@ -39319,28 +39527,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4565501333698372</v>
+        <v>-0.4449501967578528</v>
       </c>
       <c r="J2" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K2" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1284249097856757</v>
+        <v>0.1233017887931519</v>
       </c>
       <c r="M2" t="n">
-        <v>7.183847231275743</v>
+        <v>7.198935854671369</v>
       </c>
       <c r="N2" t="n">
-        <v>75.75921268216626</v>
+        <v>75.93153980301906</v>
       </c>
       <c r="O2" t="n">
-        <v>8.703976831435517</v>
+        <v>8.713870540868683</v>
       </c>
       <c r="P2" t="n">
-        <v>342.6115809980853</v>
+        <v>342.4876171201009</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39397,28 +39605,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1915249869720543</v>
+        <v>-0.1903421414949485</v>
       </c>
       <c r="J3" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K3" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09122675154793602</v>
+        <v>0.09120646032846591</v>
       </c>
       <c r="M3" t="n">
-        <v>3.713357223732543</v>
+        <v>3.698707471817864</v>
       </c>
       <c r="N3" t="n">
-        <v>19.56983532125239</v>
+        <v>19.47279040882646</v>
       </c>
       <c r="O3" t="n">
-        <v>4.42378065926108</v>
+        <v>4.412798478157196</v>
       </c>
       <c r="P3" t="n">
-        <v>337.9790379242814</v>
+        <v>337.9664032664939</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39475,28 +39683,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1553662935713178</v>
+        <v>-0.1498686191438313</v>
       </c>
       <c r="J4" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K4" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03335080034615356</v>
+        <v>0.03137854657513828</v>
       </c>
       <c r="M4" t="n">
-        <v>5.079454366324732</v>
+        <v>5.07723563768377</v>
       </c>
       <c r="N4" t="n">
-        <v>37.46961323611622</v>
+        <v>37.39911533135078</v>
       </c>
       <c r="O4" t="n">
-        <v>6.12124278526152</v>
+        <v>6.115481610744225</v>
       </c>
       <c r="P4" t="n">
-        <v>342.0499800889781</v>
+        <v>341.9912293039101</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39553,28 +39761,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05799790207686966</v>
+        <v>-0.05279925413233593</v>
       </c>
       <c r="J5" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K5" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009113946887972846</v>
+        <v>0.007614431149817746</v>
       </c>
       <c r="M5" t="n">
-        <v>3.465603741787665</v>
+        <v>3.473113733952594</v>
       </c>
       <c r="N5" t="n">
-        <v>19.58595514396578</v>
+        <v>19.59824617113971</v>
       </c>
       <c r="O5" t="n">
-        <v>4.42560223517272</v>
+        <v>4.426990645025095</v>
       </c>
       <c r="P5" t="n">
-        <v>356.3495729598924</v>
+        <v>356.2940195698822</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39631,28 +39839,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2155896065209582</v>
+        <v>-0.2072592310112005</v>
       </c>
       <c r="J6" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K6" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07697843634159096</v>
+        <v>0.07173377291718153</v>
       </c>
       <c r="M6" t="n">
-        <v>4.283495303825168</v>
+        <v>4.308521338997092</v>
       </c>
       <c r="N6" t="n">
-        <v>29.84704678463998</v>
+        <v>29.98439556092963</v>
       </c>
       <c r="O6" t="n">
-        <v>5.46324507821496</v>
+        <v>5.475800905888529</v>
       </c>
       <c r="P6" t="n">
-        <v>350.1758971703543</v>
+        <v>350.0868715777918</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39709,28 +39917,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2815748765461854</v>
+        <v>-0.2739844705434327</v>
       </c>
       <c r="J7" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K7" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1237367422452729</v>
+        <v>0.118368955834631</v>
       </c>
       <c r="M7" t="n">
-        <v>4.256027241587218</v>
+        <v>4.270847323317834</v>
       </c>
       <c r="N7" t="n">
-        <v>30.06953370136938</v>
+        <v>30.1591856294822</v>
       </c>
       <c r="O7" t="n">
-        <v>5.483569430705641</v>
+        <v>5.491737942535332</v>
       </c>
       <c r="P7" t="n">
-        <v>344.3981899347325</v>
+        <v>344.3170782717257</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39787,28 +39995,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1264236289668675</v>
+        <v>-0.1254955100304002</v>
       </c>
       <c r="J8" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K8" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03128982863644847</v>
+        <v>0.03120114380114247</v>
       </c>
       <c r="M8" t="n">
-        <v>4.03657543304026</v>
+        <v>4.023971538629202</v>
       </c>
       <c r="N8" t="n">
-        <v>26.50026059396843</v>
+        <v>26.377773547713</v>
       </c>
       <c r="O8" t="n">
-        <v>5.147840381555009</v>
+        <v>5.135929667325381</v>
       </c>
       <c r="P8" t="n">
-        <v>340.898052733855</v>
+        <v>340.8881531214595</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -39865,28 +40073,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0403859913505602</v>
+        <v>0.03916076496096819</v>
       </c>
       <c r="J9" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K9" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004201145604202927</v>
+        <v>0.00399906943914019</v>
       </c>
       <c r="M9" t="n">
-        <v>3.497053478731873</v>
+        <v>3.482656590254158</v>
       </c>
       <c r="N9" t="n">
-        <v>20.70467171931783</v>
+        <v>20.60258856133866</v>
       </c>
       <c r="O9" t="n">
-        <v>4.550238644216129</v>
+        <v>4.53900744230924</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8231223975054</v>
+        <v>343.8362241148018</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39943,28 +40151,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05189888569451694</v>
+        <v>0.05316712838734801</v>
       </c>
       <c r="J10" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K10" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0106885733898473</v>
+        <v>0.01134489840959008</v>
       </c>
       <c r="M10" t="n">
-        <v>2.941199041489277</v>
+        <v>2.931195172062939</v>
       </c>
       <c r="N10" t="n">
-        <v>13.35156925716607</v>
+        <v>13.28768323165723</v>
       </c>
       <c r="O10" t="n">
-        <v>3.653979920191964</v>
+        <v>3.64522745952255</v>
       </c>
       <c r="P10" t="n">
-        <v>349.0041597056809</v>
+        <v>348.9906025350099</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40021,28 +40229,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.008812206262603919</v>
+        <v>0.01054298732747618</v>
       </c>
       <c r="J11" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="K11" t="n">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003282487896348885</v>
+        <v>0.0004751967004225088</v>
       </c>
       <c r="M11" t="n">
-        <v>2.738315799592853</v>
+        <v>2.732137586018701</v>
       </c>
       <c r="N11" t="n">
-        <v>12.66562305902352</v>
+        <v>12.61148377789376</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55887946677371</v>
+        <v>3.551265095412304</v>
       </c>
       <c r="P11" t="n">
-        <v>357.4528278108963</v>
+        <v>357.4343304340651</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40080,7 +40288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L743"/>
+  <dimension ref="A1:L747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86149,6 +86357,254 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-01 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>-39.85772176222263,176.98571568759021</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>-39.85804064583838,176.9849120272682</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>-39.85847891850159,176.9842066554714</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>-39.859017087867954,176.98364774626828</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>-39.85953185556795,176.98305485994274</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>-39.86005806685269,176.98246171703423</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>-39.86061415954661,176.9819227481282</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>-39.86121225015092,176.9814651196397</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>-39.861853820111975,176.9811186064499</t>
+        </is>
+      </c>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>-39.86250066699532,176.98080425354976</t>
+        </is>
+      </c>
+      <c r="L744" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:14+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>-39.85771812575911,176.98571245364045</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>-39.85803819678029,176.9849098493094</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>-39.85848013132049,176.9842078647004</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>-39.85901416920758,176.9836434589457</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>-39.85953050693792,176.9830522382039</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>-39.860052181027704,176.98244983334445</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>-39.86060494215186,176.98190337745754</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>-39.86120656281974,176.98145159086542</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>-39.86185247878737,176.98111490945587</t>
+        </is>
+      </c>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>-39.86249745413959,176.98079524800082</t>
+        </is>
+      </c>
+      <c r="L745" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:25+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>-39.857710778618184,176.985705919743</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>-39.858032482311216,176.98490476740622</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>-39.85847406722588,176.9842018185559</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>-39.859010357079526,176.98363785917792</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>-39.859527410083544,176.98304621791502</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>-39.86004731670853,176.98244001211475</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>-39.860596244709484,176.98188509949603</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>-39.861205916531986,176.98145005350486</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>-39.86185278537586,176.98111575448306</t>
+        </is>
+      </c>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>-39.862497076156515,176.98079418852453</t>
+        </is>
+      </c>
+      <c r="L746" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-25 21:54:12+00:00</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>-39.857705880523994,176.98570156381217</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>-39.85802943954186,176.98490206145811</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>-39.85847157024563,176.9841993289673</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>-39.859008034063834,176.98363444681974</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>-39.859526810692344,176.98304505269786</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>-39.86004673299017,176.98243883356727</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>-39.86059326678012,176.98187884128197</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>-39.86120445161303,176.98144656882099</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>-39.86185634946658,176.98112557792473</t>
+        </is>
+      </c>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>-39.86250028901233,176.9808031940734</t>
+        </is>
+      </c>
+      <c r="L747" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L747"/>
+  <dimension ref="A1:L751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31822,6 +31822,174 @@
       <c r="L747" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="n">
+        <v>339.08</v>
+      </c>
+      <c r="C748" t="n">
+        <v>332.63</v>
+      </c>
+      <c r="D748" t="n">
+        <v>342.23</v>
+      </c>
+      <c r="E748" t="n">
+        <v>358.63</v>
+      </c>
+      <c r="F748" t="n">
+        <v>351.69</v>
+      </c>
+      <c r="G748" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="H748" t="n">
+        <v>335.8</v>
+      </c>
+      <c r="I748" t="n">
+        <v>342.39</v>
+      </c>
+      <c r="J748" t="n">
+        <v>352.97</v>
+      </c>
+      <c r="K748" t="n">
+        <v>359.91</v>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="C749" t="n">
+        <v>331.39</v>
+      </c>
+      <c r="D749" t="n">
+        <v>340.61</v>
+      </c>
+      <c r="E749" t="n">
+        <v>357.82</v>
+      </c>
+      <c r="F749" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="G749" t="n">
+        <v>341.87</v>
+      </c>
+      <c r="H749" t="n">
+        <v>333.02</v>
+      </c>
+      <c r="I749" t="n">
+        <v>341.15</v>
+      </c>
+      <c r="J749" t="n">
+        <v>352.47</v>
+      </c>
+      <c r="K749" t="n">
+        <v>359.7</v>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="C750" t="n">
+        <v>331.03</v>
+      </c>
+      <c r="D750" t="n">
+        <v>340.4</v>
+      </c>
+      <c r="E750" t="n">
+        <v>357.7</v>
+      </c>
+      <c r="F750" t="n">
+        <v>350.65</v>
+      </c>
+      <c r="G750" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="H750" t="n">
+        <v>332.76</v>
+      </c>
+      <c r="I750" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="J750" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="K750" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:34+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>333.46</v>
+      </c>
+      <c r="C751" t="n">
+        <v>330.61</v>
+      </c>
+      <c r="D751" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="E751" t="n">
+        <v>357.11</v>
+      </c>
+      <c r="F751" t="n">
+        <v>350.45</v>
+      </c>
+      <c r="G751" t="n">
+        <v>341.95</v>
+      </c>
+      <c r="H751" t="n">
+        <v>331.34</v>
+      </c>
+      <c r="I751" t="n">
+        <v>339.88</v>
+      </c>
+      <c r="J751" t="n">
+        <v>353.12</v>
+      </c>
+      <c r="K751" t="n">
+        <v>360.58</v>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -31836,7 +32004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B752"/>
+  <dimension ref="A1:B756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39359,6 +39527,46 @@
       </c>
       <c r="B752" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-05-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -39527,28 +39735,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4449501967578528</v>
+        <v>-0.4387977410978469</v>
       </c>
       <c r="J2" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K2" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1233017887931519</v>
+        <v>0.1213821575233839</v>
       </c>
       <c r="M2" t="n">
-        <v>7.198935854671369</v>
+        <v>7.188651418004949</v>
       </c>
       <c r="N2" t="n">
-        <v>75.93153980301906</v>
+        <v>75.71274962262424</v>
       </c>
       <c r="O2" t="n">
-        <v>8.713870540868683</v>
+        <v>8.701307351348087</v>
       </c>
       <c r="P2" t="n">
-        <v>342.4876171201009</v>
+        <v>342.421676413597</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39605,28 +39813,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1903421414949485</v>
+        <v>-0.1919446762481321</v>
       </c>
       <c r="J3" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K3" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09120646032846591</v>
+        <v>0.0935938497851948</v>
       </c>
       <c r="M3" t="n">
-        <v>3.698707471817864</v>
+        <v>3.687234190950301</v>
       </c>
       <c r="N3" t="n">
-        <v>19.47279040882646</v>
+        <v>19.383078775259</v>
       </c>
       <c r="O3" t="n">
-        <v>4.412798478157196</v>
+        <v>4.402621806975816</v>
       </c>
       <c r="P3" t="n">
-        <v>337.9664032664939</v>
+        <v>337.9835886264884</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39683,28 +39891,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1498686191438313</v>
+        <v>-0.1469045442230955</v>
       </c>
       <c r="J4" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K4" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03137854657513828</v>
+        <v>0.03051824179577267</v>
       </c>
       <c r="M4" t="n">
-        <v>5.07723563768377</v>
+        <v>5.063676377837218</v>
       </c>
       <c r="N4" t="n">
-        <v>37.39911533135078</v>
+        <v>37.24308761901718</v>
       </c>
       <c r="O4" t="n">
-        <v>6.115481610744225</v>
+        <v>6.102711497278663</v>
       </c>
       <c r="P4" t="n">
-        <v>341.9912293039101</v>
+        <v>341.9594610805009</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39761,28 +39969,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05279925413233593</v>
+        <v>-0.04957782011211853</v>
       </c>
       <c r="J5" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K5" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007614431149817746</v>
+        <v>0.006787029180032933</v>
       </c>
       <c r="M5" t="n">
-        <v>3.473113733952594</v>
+        <v>3.470719058757564</v>
       </c>
       <c r="N5" t="n">
-        <v>19.59824617113971</v>
+        <v>19.54036209718504</v>
       </c>
       <c r="O5" t="n">
-        <v>4.426990645025095</v>
+        <v>4.420448178316883</v>
       </c>
       <c r="P5" t="n">
-        <v>356.2940195698822</v>
+        <v>356.2594889123536</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39839,28 +40047,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2072592310112005</v>
+        <v>-0.2003534957321667</v>
       </c>
       <c r="J6" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K6" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07173377291718153</v>
+        <v>0.06769385114012816</v>
       </c>
       <c r="M6" t="n">
-        <v>4.308521338997092</v>
+        <v>4.325149055047948</v>
       </c>
       <c r="N6" t="n">
-        <v>29.98439556092963</v>
+        <v>30.03296856469785</v>
       </c>
       <c r="O6" t="n">
-        <v>5.475800905888529</v>
+        <v>5.480234353081796</v>
       </c>
       <c r="P6" t="n">
-        <v>350.0868715777918</v>
+        <v>350.0128431502307</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39917,28 +40125,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2739844705434327</v>
+        <v>-0.2681715382233688</v>
       </c>
       <c r="J7" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K7" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L7" t="n">
-        <v>0.118368955834631</v>
+        <v>0.114727566874945</v>
       </c>
       <c r="M7" t="n">
-        <v>4.270847323317834</v>
+        <v>4.276982824127611</v>
       </c>
       <c r="N7" t="n">
-        <v>30.1591856294822</v>
+        <v>30.14599411984883</v>
       </c>
       <c r="O7" t="n">
-        <v>5.491737942535332</v>
+        <v>5.490536778844928</v>
       </c>
       <c r="P7" t="n">
-        <v>344.3170782717257</v>
+        <v>344.2547641902255</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39995,28 +40203,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1254955100304002</v>
+        <v>-0.1302165381299879</v>
       </c>
       <c r="J8" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K8" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03120114380114247</v>
+        <v>0.03378012102694916</v>
       </c>
       <c r="M8" t="n">
-        <v>4.023971538629202</v>
+        <v>4.021780740404515</v>
       </c>
       <c r="N8" t="n">
-        <v>26.377773547713</v>
+        <v>26.34766567324057</v>
       </c>
       <c r="O8" t="n">
-        <v>5.135929667325381</v>
+        <v>5.132997727764992</v>
       </c>
       <c r="P8" t="n">
-        <v>340.8881531214595</v>
+        <v>340.9387765378354</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40073,28 +40281,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03916076496096819</v>
+        <v>0.03484728297748312</v>
       </c>
       <c r="J9" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K9" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00399906943914019</v>
+        <v>0.003195474990958402</v>
       </c>
       <c r="M9" t="n">
-        <v>3.482656590254158</v>
+        <v>3.47899209932972</v>
       </c>
       <c r="N9" t="n">
-        <v>20.60258856133866</v>
+        <v>20.57820590127696</v>
       </c>
       <c r="O9" t="n">
-        <v>4.53900744230924</v>
+        <v>4.536320744973503</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8362241148018</v>
+        <v>343.8824731939695</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40151,28 +40359,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05316712838734801</v>
+        <v>0.05585505854218097</v>
       </c>
       <c r="J10" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K10" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01134489840959008</v>
+        <v>0.01263086549062065</v>
       </c>
       <c r="M10" t="n">
-        <v>2.931195172062939</v>
+        <v>2.92772966262679</v>
       </c>
       <c r="N10" t="n">
-        <v>13.28768323165723</v>
+        <v>13.24849498564008</v>
       </c>
       <c r="O10" t="n">
-        <v>3.64522745952255</v>
+        <v>3.639848209148299</v>
       </c>
       <c r="P10" t="n">
-        <v>348.9906025350099</v>
+        <v>348.9617865289143</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40229,28 +40437,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01054298732747618</v>
+        <v>0.01313423581132506</v>
       </c>
       <c r="J11" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="K11" t="n">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004751967004225088</v>
+        <v>0.0007447485155905875</v>
       </c>
       <c r="M11" t="n">
-        <v>2.732137586018701</v>
+        <v>2.730259345838843</v>
       </c>
       <c r="N11" t="n">
-        <v>12.61148377789376</v>
+        <v>12.57394331253739</v>
       </c>
       <c r="O11" t="n">
-        <v>3.551265095412304</v>
+        <v>3.545975650302381</v>
       </c>
       <c r="P11" t="n">
-        <v>357.4343304340651</v>
+        <v>357.4065494317818</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40288,7 +40496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L747"/>
+  <dimension ref="A1:L751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86605,6 +86813,254 @@
         </is>
       </c>
     </row>
+    <row r="748">
+      <c r="A748" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-02 22:00:18+00:00</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>-39.85770083400249,176.9856970758841</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>-39.85802550620574,176.98489856352558</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>-39.858471712930225,176.98419947122952</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>-39.85900731928976,176.98363339686344</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>-39.85952795952548,176.98304728603074</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>-39.86004707349256,176.98243952105332</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>-39.86059005250676,176.98187208638484</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>-39.86120122017374,176.98143888201886</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>-39.86185937702681,176.9811339225695</t>
+        </is>
+      </c>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>-39.86250138516297,176.98080626655494</t>
+        </is>
+      </c>
+      <c r="L748" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-10 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>-39.85768228061281,176.98568057615438</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>-39.858016303683016,176.984890379685</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>-39.858460155478035,176.98418794799318</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>-39.859002494564436,176.98362630965886</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>-39.85952211546077,176.98303592516427</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>-39.860042063242815,176.98242940518819</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>-39.86057691179648,176.98184447078236</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>-39.861195877526235,176.98142617317416</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>-39.861857460849514,176.9811286411487</t>
+        </is>
+      </c>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>-39.862500591398714,176.9808040416545</t>
+        </is>
+      </c>
+      <c r="L749" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-11 21:53:59+00:00</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>-39.85767508189685,176.9856741742617</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>-39.85801363198275,176.98488800373173</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>-39.85845865728969,176.98418645424061</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>-39.859001779790276,176.9836252597027</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>-39.85952276480135,176.9830371874827</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>-39.86004454404621,176.98243441401442</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>-39.86057568280882,176.98184188802873</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>-39.86119268917137,176.9814185888645</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>-39.861859032114914,176.98113297191375</t>
+        </is>
+      </c>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>-39.86250214112888,176.98080838550777</t>
+        </is>
+      </c>
+      <c r="L750" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-19 21:53:34+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>-39.85765912597853,176.98565998450448</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>-39.85801051499902,176.98488523178645</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>-39.858452022455296,176.98417983905148</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>-39.858998265483805,176.98362009741862</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>-39.859521765815835,176.9830352454544</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>-39.86004245238847,176.98243019088642</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>-39.86056897064437,176.9818277822218</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>-39.86119040561958,176.98141315685936</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>-39.86185995187994,176.9811355069958</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>-39.8625039176486,176.98081336504717</t>
+        </is>
+      </c>
+      <c r="L751" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0298/nzd0298.xlsx
+++ b/data/nzd0298/nzd0298.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L751"/>
+  <dimension ref="A1:L755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31990,6 +31990,174 @@
       <c r="L751" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:59:43+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="C752" t="n">
+        <v>330.39</v>
+      </c>
+      <c r="D752" t="n">
+        <v>339.03</v>
+      </c>
+      <c r="E752" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="F752" t="n">
+        <v>350.4</v>
+      </c>
+      <c r="G752" t="n">
+        <v>342.09</v>
+      </c>
+      <c r="H752" t="n">
+        <v>331.01</v>
+      </c>
+      <c r="I752" t="n">
+        <v>339.31</v>
+      </c>
+      <c r="J752" t="n">
+        <v>352.77</v>
+      </c>
+      <c r="K752" t="n">
+        <v>360.82</v>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:29+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>330.52</v>
+      </c>
+      <c r="C753" t="n">
+        <v>329.82</v>
+      </c>
+      <c r="D753" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="E753" t="n">
+        <v>355.74</v>
+      </c>
+      <c r="F753" t="n">
+        <v>349.92</v>
+      </c>
+      <c r="G753" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="H753" t="n">
+        <v>329.7</v>
+      </c>
+      <c r="I753" t="n">
+        <v>338.11</v>
+      </c>
+      <c r="J753" t="n">
+        <v>352.7</v>
+      </c>
+      <c r="K753" t="n">
+        <v>360.74</v>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>329.24</v>
+      </c>
+      <c r="C754" t="n">
+        <v>329.59</v>
+      </c>
+      <c r="D754" t="n">
+        <v>338.24</v>
+      </c>
+      <c r="E754" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="F754" t="n">
+        <v>349.77</v>
+      </c>
+      <c r="G754" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="H754" t="n">
+        <v>330</v>
+      </c>
+      <c r="I754" t="n">
+        <v>338.1</v>
+      </c>
+      <c r="J754" t="n">
+        <v>352.71</v>
+      </c>
+      <c r="K754" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>329.97</v>
+      </c>
+      <c r="C755" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D755" t="n">
+        <v>338</v>
+      </c>
+      <c r="E755" t="n">
+        <v>354.88</v>
+      </c>
+      <c r="F755" t="n">
+        <v>349.68</v>
+      </c>
+      <c r="G755" t="n">
+        <v>341.07</v>
+      </c>
+      <c r="H755" t="n">
+        <v>330.55</v>
+      </c>
+      <c r="I755" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="J755" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="K755" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -32004,7 +32172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B756"/>
+  <dimension ref="A1:B760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39567,6 +39735,46 @@
       </c>
       <c r="B756" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-05-26 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-06-03 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-06-11 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -39735,28 +39943,28 @@
         <v>0.042</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.4387977410978469</v>
+        <v>-0.439007986401406</v>
       </c>
       <c r="J2" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K2" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1213821575233839</v>
+        <v>0.1227949045490682</v>
       </c>
       <c r="M2" t="n">
-        <v>7.188651418004949</v>
+        <v>7.155395226707337</v>
       </c>
       <c r="N2" t="n">
-        <v>75.71274962262424</v>
+        <v>75.31704687597419</v>
       </c>
       <c r="O2" t="n">
-        <v>8.701307351348087</v>
+        <v>8.678539443706768</v>
       </c>
       <c r="P2" t="n">
-        <v>342.421676413597</v>
+        <v>342.4239454632108</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39813,28 +40021,28 @@
         <v>0.0539</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1919446762481321</v>
+        <v>-0.1951018715542421</v>
       </c>
       <c r="J3" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K3" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0935938497851948</v>
+        <v>0.09727323581817848</v>
       </c>
       <c r="M3" t="n">
-        <v>3.687234190950301</v>
+        <v>3.683759831379467</v>
       </c>
       <c r="N3" t="n">
-        <v>19.383078775259</v>
+        <v>19.32473148367772</v>
       </c>
       <c r="O3" t="n">
-        <v>4.402621806975816</v>
+        <v>4.395990387122988</v>
       </c>
       <c r="P3" t="n">
-        <v>337.9835886264884</v>
+        <v>338.0175329279596</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39891,28 +40099,28 @@
         <v>0.0515</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1469045442230955</v>
+        <v>-0.146455363829572</v>
       </c>
       <c r="J4" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K4" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03051824179577267</v>
+        <v>0.0307002110247836</v>
       </c>
       <c r="M4" t="n">
-        <v>5.063676377837218</v>
+        <v>5.038917365868932</v>
       </c>
       <c r="N4" t="n">
-        <v>37.24308761901718</v>
+        <v>37.0471635938075</v>
       </c>
       <c r="O4" t="n">
-        <v>6.102711497278663</v>
+        <v>6.086638119176094</v>
       </c>
       <c r="P4" t="n">
-        <v>341.9594610805009</v>
+        <v>341.9546353315924</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39969,28 +40177,28 @@
         <v>0.0559</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04957782011211853</v>
+        <v>-0.04879707336245043</v>
       </c>
       <c r="J5" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K5" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006787029180032933</v>
+        <v>0.006655456051401942</v>
       </c>
       <c r="M5" t="n">
-        <v>3.470719058757564</v>
+        <v>3.456357307860996</v>
       </c>
       <c r="N5" t="n">
-        <v>19.54036209718504</v>
+        <v>19.44183637080527</v>
       </c>
       <c r="O5" t="n">
-        <v>4.420448178316883</v>
+        <v>4.409289780770285</v>
       </c>
       <c r="P5" t="n">
-        <v>356.2594889123536</v>
+        <v>356.2511012274655</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -40047,28 +40255,28 @@
         <v>0.0465</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2003534957321667</v>
+        <v>-0.1945891586947628</v>
       </c>
       <c r="J6" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K6" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06769385114012816</v>
+        <v>0.06454516762294193</v>
       </c>
       <c r="M6" t="n">
-        <v>4.325149055047948</v>
+        <v>4.335199015899225</v>
       </c>
       <c r="N6" t="n">
-        <v>30.03296856469785</v>
+        <v>30.02092103389892</v>
       </c>
       <c r="O6" t="n">
-        <v>5.480234353081796</v>
+        <v>5.479135062571365</v>
       </c>
       <c r="P6" t="n">
-        <v>350.0128431502307</v>
+        <v>349.9508746016546</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -40125,28 +40333,28 @@
         <v>0.047</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2681715382233688</v>
+        <v>-0.2633744070052741</v>
       </c>
       <c r="J7" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K7" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L7" t="n">
-        <v>0.114727566874945</v>
+        <v>0.1119927889991305</v>
       </c>
       <c r="M7" t="n">
-        <v>4.276982824127611</v>
+        <v>4.27811666795616</v>
       </c>
       <c r="N7" t="n">
-        <v>30.14599411984883</v>
+        <v>30.08854696995111</v>
       </c>
       <c r="O7" t="n">
-        <v>5.490536778844928</v>
+        <v>5.485302814790731</v>
       </c>
       <c r="P7" t="n">
-        <v>344.2547641902255</v>
+        <v>344.2031946875757</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -40203,28 +40411,28 @@
         <v>0.0509</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1302165381299879</v>
+        <v>-0.137958068383621</v>
       </c>
       <c r="J8" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K8" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03378012102694916</v>
+        <v>0.03783975488709912</v>
       </c>
       <c r="M8" t="n">
-        <v>4.021780740404515</v>
+        <v>4.032100674518665</v>
       </c>
       <c r="N8" t="n">
-        <v>26.34766567324057</v>
+        <v>26.47408418585983</v>
       </c>
       <c r="O8" t="n">
-        <v>5.132997727764992</v>
+        <v>5.145297288384786</v>
       </c>
       <c r="P8" t="n">
-        <v>340.9387765378354</v>
+        <v>341.0220056870387</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -40281,28 +40489,28 @@
         <v>0.0505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03484728297748312</v>
+        <v>0.02801752302243645</v>
       </c>
       <c r="J9" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K9" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003195474990958402</v>
+        <v>0.002072574222526935</v>
       </c>
       <c r="M9" t="n">
-        <v>3.47899209932972</v>
+        <v>3.484235574239093</v>
       </c>
       <c r="N9" t="n">
-        <v>20.57820590127696</v>
+        <v>20.67645033243967</v>
       </c>
       <c r="O9" t="n">
-        <v>4.536320744973503</v>
+        <v>4.547136498109515</v>
       </c>
       <c r="P9" t="n">
-        <v>343.8824731939695</v>
+        <v>343.9559011415</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40359,28 +40567,28 @@
         <v>0.0556</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05585505854218097</v>
+        <v>0.05833062867040802</v>
       </c>
       <c r="J10" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K10" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01263086549062065</v>
+        <v>0.01389932906713742</v>
       </c>
       <c r="M10" t="n">
-        <v>2.92772966262679</v>
+        <v>2.923434385894742</v>
       </c>
       <c r="N10" t="n">
-        <v>13.24849498564008</v>
+        <v>13.20530307487388</v>
       </c>
       <c r="O10" t="n">
-        <v>3.639848209148299</v>
+        <v>3.633910163291585</v>
       </c>
       <c r="P10" t="n">
-        <v>348.9617865289143</v>
+        <v>348.9351723543862</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40437,28 +40645,28 @@
         <v>0.0504</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01313423581132506</v>
+        <v>0.01632416179054414</v>
       </c>
       <c r="J11" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="K11" t="n">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0007447485155905875</v>
+        <v>0.001160014805233978</v>
       </c>
       <c r="M11" t="n">
-        <v>2.730259345838843</v>
+        <v>2.731496835510873</v>
       </c>
       <c r="N11" t="n">
-        <v>12.57394331253739</v>
+        <v>12.55225663182004</v>
       </c>
       <c r="O11" t="n">
-        <v>3.545975650302381</v>
+        <v>3.54291640203661</v>
       </c>
       <c r="P11" t="n">
-        <v>357.4065494317818</v>
+        <v>357.3722561347764</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40496,7 +40704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L751"/>
+  <dimension ref="A1:L755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87061,6 +87269,254 @@
         </is>
       </c>
     </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26 21:59:43+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>-39.85764903293142,176.98565100866156</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>-39.85800888229322,176.98488377981522</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>-39.85844888339372,176.98417670928504</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>-39.85899582333849,176.98361651006897</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>-39.85952151606945,176.98303475994732</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>-39.86004313339333,176.9824315658583</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>-39.8605674107749,176.98182450411213</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>-39.86118794972398,176.98140731489195</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>-39.86185861055593,176.98113181000116</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>-39.86250482480751,176.98081590779077</t>
+        </is>
+      </c>
+      <c r="L752" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-03 21:59:29+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>-39.85763730718446,176.9856405808474</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>-39.85800465210083,176.9848800178901</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>-39.85844481688196,176.9841726548153</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>-39.85899010514407,176.983608110422</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>-39.85951911850403,176.98303009907966</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>-39.86004011751451,176.98242547669727</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>-39.8605612185648,176.98181149101154</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>-39.86118277941636,176.98139501601452</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>-39.8618583422911,176.98113107060223</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>-39.862504522421226,176.98081506020955</t>
+        </is>
+      </c>
+      <c r="L753" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-11 21:59:21+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>-39.85762780784433,176.98563213300062</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>-39.858002945181056,176.98487849992046</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>-39.85844324735107,176.98417108993235</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>-39.85898736517568,176.98360408559165</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>-39.85951836926479,176.98302864255857</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>-39.86003919329351,176.98242361066414</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>-39.860562636628316,176.9818144711107</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>-39.861182736330456,176.98139491352387</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>-39.86185838061465,176.98113117623063</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>-39.862504106640046,176.9808138947854</t>
+        </is>
+      </c>
+      <c r="L754" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-12 21:53:46+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>-39.85763322543684,176.98563695091295</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>-39.85800524581205,176.98488054587955</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>-39.858441535135526,176.98416938278743</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>-39.85898498259434,176.98360058573945</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>-39.85951791972126,176.98302776864594</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>-39.86003817178605,176.9824215482066</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>-39.860565236411226,176.98181993462617</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>-39.861184890625466,176.9814000380559</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>-39.86185864887947,176.98113191562956</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>-39.86250399324517,176.98081357694247</t>
+        </is>
+      </c>
+      <c r="L755" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
